--- a/settings.xlsx
+++ b/settings.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="141">
   <si>
     <t>Section</t>
   </si>
@@ -127,7 +127,7 @@
     <t>sample_tags</t>
   </si>
   <si>
-    <t>Include extra group:</t>
+    <t>Include all files:</t>
   </si>
   <si>
     <t>False</t>
@@ -145,7 +145,7 @@
     <t>ANALYSIS SETTINGS</t>
   </si>
   <si>
-    <t>Noise threshold:</t>
+    <t>Maximum background noise:</t>
   </si>
   <si>
     <t>Number. 
@@ -235,7 +235,7 @@
     <t>DATA LENGTH / TAIL CUTTING</t>
   </si>
   <si>
-    <t>Sampling interval:</t>
+    <t>Length of Lumi's interval:</t>
   </si>
   <si>
     <t>Positive number. 
@@ -248,70 +248,49 @@
     <t>interval_minutes</t>
   </si>
   <si>
-    <t>Maximum rows:</t>
+    <t>Maximum days:</t>
+  </si>
+  <si>
+    <t>Positive number, or None.</t>
+  </si>
+  <si>
+    <t>Optional: limit analysis to the first N days after alignment. Use only one of max_rows, max_hours, max_days. Leave all as None to keep the full data.</t>
+  </si>
+  <si>
+    <t>max_days</t>
+  </si>
+  <si>
+    <t>PLOTTING SETTINGS</t>
+  </si>
+  <si>
+    <t>Create plots of the data:</t>
+  </si>
+  <si>
+    <t>True = create and save raw-data plots. False = do not create raw-data plots.</t>
+  </si>
+  <si>
+    <t>plot_raw_data</t>
+  </si>
+  <si>
+    <t>Choose plot style:</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>points / line / points+line</t>
+  </si>
+  <si>
+    <t>Plot display style. points = plot data as points only. line = plot data as continuous lines. points+line = plot points connected by lines.</t>
+  </si>
+  <si>
+    <t>plot_style</t>
+  </si>
+  <si>
+    <t>Y-axis upper limit:</t>
   </si>
   <si>
     <t>None</t>
-  </si>
-  <si>
-    <t>Positive integer, or None.</t>
-  </si>
-  <si>
-    <t>Optional: limit analysis to the first N rows after alignment. Use only one of max_rows, max_hours, max_days. Leave all as None to keep the full data.</t>
-  </si>
-  <si>
-    <t>max_rows</t>
-  </si>
-  <si>
-    <t>Maximum hours:</t>
-  </si>
-  <si>
-    <t>Positive number, or None.</t>
-  </si>
-  <si>
-    <t>Optional: limit analysis to the first N hours after alignment. Use only one of max_rows, max_hours, max_days. Leave all as None to keep the full data.</t>
-  </si>
-  <si>
-    <t>max_hours</t>
-  </si>
-  <si>
-    <t>Maximum days:</t>
-  </si>
-  <si>
-    <t>Optional: limit analysis to the first N days after alignment. Use only one of max_rows, max_hours, max_days. Leave all as None to keep the full data.</t>
-  </si>
-  <si>
-    <t>max_days</t>
-  </si>
-  <si>
-    <t>PLOTTING SETTINGS</t>
-  </si>
-  <si>
-    <t>Create raw-data plots:</t>
-  </si>
-  <si>
-    <t>True = create and save raw-data plots. False = do not create raw-data plots.</t>
-  </si>
-  <si>
-    <t>plot_raw_data</t>
-  </si>
-  <si>
-    <t>Plot style:</t>
-  </si>
-  <si>
-    <t>line</t>
-  </si>
-  <si>
-    <t>points / line / points+line</t>
-  </si>
-  <si>
-    <t>Plot display style. points = plot data as points only. line = plot data as continuous lines. points+line = plot points connected by lines.</t>
-  </si>
-  <si>
-    <t>plot_style</t>
-  </si>
-  <si>
-    <t>Y-axis limit:</t>
   </si>
   <si>
     <t>None, a number, or a tuple. 
@@ -324,22 +303,6 @@
     <t>y_limit</t>
   </si>
   <si>
-    <t>Figure size:</t>
-  </si>
-  <si>
-    <t>(9, 5)</t>
-  </si>
-  <si>
-    <t>Tuple of two numbers: (width, height). 
-Example: (9, 5)</t>
-  </si>
-  <si>
-    <t>Figure size in inches.</t>
-  </si>
-  <si>
-    <t>figsize</t>
-  </si>
-  <si>
     <t>Plot description:</t>
   </si>
   <si>
@@ -353,28 +316,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>Replicates used for mean:</t>
-  </si>
-  <si>
-    <t>None, empty list [], or list of replicate names. 
-Example: ["c i", "c iii"]</t>
-  </si>
-  <si>
-    <t>Controls which replicates are included in the average. None = use all replicate columns automatically.</t>
-  </si>
-  <si>
-    <t>mean_replicate_cols</t>
-  </si>
-  <si>
-    <t>Replicates shown on plot:</t>
-  </si>
-  <si>
-    <t>Controls which replicates are shown on the plot. None = show all replicate columns automatically. An empty list can be used to show only the average curve/points.</t>
-  </si>
-  <si>
-    <t>visible_replicate_cols</t>
   </si>
   <si>
     <t>CT start hour:</t>
@@ -391,7 +332,7 @@
     <t>ct_start_hour</t>
   </si>
   <si>
-    <t>X-axis start:</t>
+    <t>X-axis start (only changes the plot):</t>
   </si>
   <si>
     <t>Number. Usually 0.</t>
@@ -415,28 +356,6 @@
     <t>plot_peaks</t>
   </si>
   <si>
-    <t>Replicate peaks to show:</t>
-  </si>
-  <si>
-    <t>Which replicate peaks to show. None = show peaks for all visible replicates. [] = show no replicate peaks.</t>
-  </si>
-  <si>
-    <t>peaks_to_show</t>
-  </si>
-  <si>
-    <t>Replicate peak labels:</t>
-  </si>
-  <si>
-    <t>None, empty list [], or list of replicate names. 
-Example: ["c iii"]</t>
-  </si>
-  <si>
-    <t>Which replicate should also get text labels next to their peaks. None or [] = no replicate has peak text labels.</t>
-  </si>
-  <si>
-    <t>peaks_to_show_txt</t>
-  </si>
-  <si>
     <t>Show average peaks:</t>
   </si>
   <si>
@@ -453,19 +372,6 @@
   </si>
   <si>
     <t>show_average_peaks_txt</t>
-  </si>
-  <si>
-    <t>Peak label vertical offset:</t>
-  </si>
-  <si>
-    <t>Number. 
-Example: 20</t>
-  </si>
-  <si>
-    <t>Vertical offset for peak text labels.</t>
-  </si>
-  <si>
-    <t>peak_txt_dy</t>
   </si>
   <si>
     <t>PEAK/PERIOD TABLE SETTINGS</t>
@@ -493,24 +399,6 @@
     <t>peak_table_decimals</t>
   </si>
   <si>
-    <t>Write periods as text:</t>
-  </si>
-  <si>
-    <t>True = period values are written as text like "(24.17 h)". False = period values are saved as numeric values.</t>
-  </si>
-  <si>
-    <t>peak_table_period_as_text</t>
-  </si>
-  <si>
-    <t>Include average in peak table:</t>
-  </si>
-  <si>
-    <t>Whether to include the average signal as an additional row.</t>
-  </si>
-  <si>
-    <t>include_average_in_peak_table</t>
-  </si>
-  <si>
     <t>GROUP-SPECIFIC OVERRIDES</t>
   </si>
   <si>
@@ -529,6 +417,9 @@
     <t>override_group_names</t>
   </si>
   <si>
+    <t>Y-axis limit:</t>
+  </si>
+  <si>
     <t>List with one value per group, or an empty position for no override. Example: [500, , (-100, 500)]</t>
   </si>
   <si>
@@ -547,6 +438,9 @@
     <t>override_description</t>
   </si>
   <si>
+    <t>Peak label vertical offset:</t>
+  </si>
+  <si>
     <t>List with one value per group, or an empty position for no override. Example: [20, , 35]</t>
   </si>
   <si>
@@ -556,6 +450,9 @@
     <t>override_peak_txt_dy</t>
   </si>
   <si>
+    <t>Replicates to disable:</t>
+  </si>
+  <si>
     <t>List with one value per group, or an empty position for no override. Example: [None, ["c i", "c iii"], ]</t>
   </si>
   <si>
@@ -563,6 +460,9 @@
   </si>
   <si>
     <t>override_mean_replicate_cols</t>
+  </si>
+  <si>
+    <t>Replicates to hide:</t>
   </si>
   <si>
     <t>List with one value per group, or an empty position for no override. Example: [None, [], ["c i"]]</t>
@@ -1017,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1337,543 +1237,363 @@
       <c r="B21" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="9">
+        <v>7</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="6" t="s">
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="9">
-        <v>7</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D24" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="E24" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="20" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="F24" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>68</v>
+        <v>90</v>
+      </c>
+      <c r="C27" s="9">
+        <v>6</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="7" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="C30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="F31" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="20" customHeight="1">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="9">
-        <v>6</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="C34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="6" t="s">
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
+      <c r="C35" s="9">
+        <v>2</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="9">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="E35" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="6" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="20" customHeight="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="20" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="D37" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="5"/>
       <c r="B40" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="9">
-        <v>20</v>
-      </c>
-      <c r="D40" s="8" t="s">
+      <c r="E41" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F41" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F40" s="6" t="s">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="20" customHeight="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5" t="s">
+      <c r="C42" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="E42" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="9">
-        <v>2</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="20" customHeight="1">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1889,17 +1609,17 @@
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:A33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:A42"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
       <formula1>"True,False"</formula1>
     </dataValidation>
@@ -1909,28 +1629,22 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"points,line,points+line"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C30">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C38">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C39">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C42">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C44">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C45">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C34">
       <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D77CF-59EF-4F18-A53E-022E7480E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="139">
   <si>
     <t>Section</t>
   </si>
@@ -61,9 +67,6 @@
   </si>
   <si>
     <t>Input folder:</t>
-  </si>
-  <si>
-    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/ORG slices contr females 13.4.26/Analysis/</t>
   </si>
   <si>
     <t>Folder path as text. 
@@ -114,9 +117,6 @@
     <t>Sample names:</t>
   </si>
   <si>
-    <t>["Liver1", "Liver2", "Kid1", "Kid2", "Lung1", "Lung2"]</t>
-  </si>
-  <si>
     <t>List of group names, or None. 
 Example: ["Liver1", "Liver2"]</t>
   </si>
@@ -130,9 +130,6 @@
     <t>Include all files:</t>
   </si>
   <si>
-    <t>False</t>
-  </si>
-  <si>
     <t>True / False</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Remove background noise:</t>
   </si>
   <si>
-    <t>True</t>
-  </si>
-  <si>
     <t>True = subtract the average pre-sample noise from the signal. False = keep the signal without subtracting that background.</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
     <t>Choose plot style:</t>
   </si>
   <si>
-    <t>line</t>
-  </si>
-  <si>
     <t>points / line / points+line</t>
   </si>
   <si>
@@ -306,9 +297,6 @@
     <t>Plot description:</t>
   </si>
   <si>
-    <t>Control (females 13.4.26)</t>
-  </si>
-  <si>
     <t>Text, or None.</t>
   </si>
   <si>
@@ -472,17 +460,29 @@
   </si>
   <si>
     <t>override_visible_replicate_cols</t>
+  </si>
+  <si>
+    <t>["10% serum", "2% serum", "20% serum", "Dex - 10% serum", "Allicin 1", "Allicin 10", "Allicin 25", "Allicin 10 (26.3)", "Allicin 25 (26.3)"]</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM2/Analysis/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -490,7 +490,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -498,7 +498,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -506,14 +506,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -521,7 +521,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -591,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -602,9 +602,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -623,19 +620,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -673,7 +684,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -707,6 +718,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -741,9 +753,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -916,17 +929,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="75.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.69921875" customWidth="1"/>
+    <col min="2" max="4" width="42.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,706 +959,685 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="8">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="9">
-        <v>5</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="96" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="C9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="C11" s="8">
+        <v>20</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="9">
-        <v>25</v>
-      </c>
-      <c r="D11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="C12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
+    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="7" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="7" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="7" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="C18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="C20" s="8">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="9">
-        <v>10</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="C21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
+    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="9">
-        <v>7</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="B23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="C23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+    <row r="24" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C24" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
+    <row r="25" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
+    <row r="26" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="E27" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="F27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="6" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="9">
-        <v>6</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="F28" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="6" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
+      <c r="C30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="9">
+      <c r="F30" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="6" t="s">
+      <c r="D31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="20" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="6" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="C32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
+    <row r="33" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="C34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="6" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="20" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="6" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+    </row>
+    <row r="37" spans="1:6" ht="204.6" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="9">
-        <v>2</v>
-      </c>
-      <c r="D35" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="20" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
+    <row r="38" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C38" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="E38" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="F38" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="6" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="8" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="C40" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="F40" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E39" s="6" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="C41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="8" t="s">
+      <c r="F41" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="6" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="C42" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="8" t="s">
+      <c r="F42" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:A42"/>
   </mergeCells>
-  <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C34 C30:C32 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C30">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C34">
-      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D77CF-59EF-4F18-A53E-022E7480E160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E18A45-D828-4AA6-8262-3AF96710CC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="146">
   <si>
     <t>Section</t>
   </si>
@@ -130,6 +130,9 @@
     <t>Include all files:</t>
   </si>
   <si>
+    <t>False</t>
+  </si>
+  <si>
     <t>True / False</t>
   </si>
   <si>
@@ -158,6 +161,9 @@
     <t>Remove background noise:</t>
   </si>
   <si>
+    <t>True</t>
+  </si>
+  <si>
     <t>True = subtract the average pre-sample noise from the signal. False = keep the signal without subtracting that background.</t>
   </si>
   <si>
@@ -266,6 +272,18 @@
     <t>plot_raw_data</t>
   </si>
   <si>
+    <t>Replicate display mode:</t>
+  </si>
+  <si>
+    <t>replicates_and_mean / mean_only / replicates_only</t>
+  </si>
+  <si>
+    <t>Choose what to display on the raw-data plots. replicates_and_mean = show both replicates and the average signal. mean_only = show only the average signal. replicates_only = show only the replicate signals, without the average.</t>
+  </si>
+  <si>
+    <t>replicate_display_mode</t>
+  </si>
+  <si>
     <t>Choose plot style:</t>
   </si>
   <si>
@@ -462,16 +480,19 @@
     <t>override_visible_replicate_cols</t>
   </si>
   <si>
+    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM2/Analysis/</t>
+  </si>
+  <si>
     <t>["10% serum", "2% serum", "20% serum", "Dex - 10% serum", "Allicin 1", "Allicin 10", "Allicin 25", "Allicin 10 (26.3)", "Allicin 25 (26.3)"]</t>
   </si>
   <si>
-    <t>points</t>
-  </si>
-  <si>
-    <t>DM2</t>
-  </si>
-  <si>
-    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM2/Analysis/</t>
+    <t>points+line</t>
+  </si>
+  <si>
+    <t>"DM2"</t>
+  </si>
+  <si>
+    <t>mean_only</t>
   </si>
 </sst>
 </file>
@@ -930,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.69921875" customWidth="1"/>
@@ -975,7 +996,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>8</v>
@@ -1049,7 +1070,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>23</v>
@@ -1066,17 +1087,17 @@
       <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="b">
-        <v>0</v>
+      <c r="C9" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1089,40 +1110,40 @@
     </row>
     <row r="11" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8">
         <v>20</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="6" t="b">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1135,58 +1156,58 @@
     </row>
     <row r="14" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1199,22 +1220,22 @@
     </row>
     <row r="18" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="6" t="b">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1227,40 +1248,40 @@
     </row>
     <row r="20" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" s="8">
         <v>10</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1273,354 +1294,372 @@
     </row>
     <row r="23" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="6" t="b">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="93" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28" s="8">
         <v>0</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="6" t="b">
+    </row>
+    <row r="29" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
+      <c r="E29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>98</v>
+      </c>
       <c r="B31" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31" s="6" t="b">
         <v>0</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C32" s="6" t="b">
         <v>0</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="5" t="s">
+    </row>
+    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
+      <c r="C33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>108</v>
+      </c>
       <c r="B35" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C35" s="8">
+        <v>109</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="8">
         <v>2</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6" ht="204.6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D37" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
+    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="204.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>116</v>
+      </c>
       <c r="B38" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
       <c r="A39" s="10"/>
       <c r="B39" s="5" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
       <c r="A40" s="10"/>
       <c r="B40" s="5" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
       <c r="B41" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="93" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:A16"/>
@@ -1632,11 +1671,14 @@
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:F10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C34 C30:C32 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"points,line,points+line"</formula1>
     </dataValidation>
   </dataValidations>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E18A45-D828-4AA6-8262-3AF96710CC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="141">
   <si>
     <t>Section</t>
   </si>
@@ -66,14 +60,38 @@
     <t>INPUT DATA</t>
   </si>
   <si>
-    <t>Input folder:</t>
-  </si>
-  <si>
-    <t>Folder path as text. 
-Example: C:/Users/.../Analysis/</t>
-  </si>
-  <si>
-    <t>Paste the path to the folder that contains the Lumi raw CSV files. The folder should contain files such as 1a_Raw.csv, 1b_Raw.csv, 2a_Raw.csv, etc.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Input folder:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Folder path as text. 
+Example: C:/Users/.../Analysis/
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Paste the path to the folder that contains the Lumi raw CSV files. The folder should contain files such as 1a_Raw.csv, 1b_Raw.csv, 2a_Raw.csv, etc.Make sure the backslashes / are in the same direction as here.
+</t>
   </si>
   <si>
     <t>input_folder</t>
@@ -82,16 +100,42 @@
     <t>OUTPUT FOLDER</t>
   </si>
   <si>
-    <t>Output folder:</t>
-  </si>
-  <si>
-    <t>test_output</t>
-  </si>
-  <si>
-    <t>Folder name or full folder path as text.</t>
-  </si>
-  <si>
-    <t>Choose the name/path of the folder where processed results will be saved. If the folder does not exist, it will be created automatically.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Output folder:</t>
+    </r>
+  </si>
+  <si>
+    <t>analysis_output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Folder name 
+or 
+Full folder path
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Choose the name/path of the folder where processed results will be saved. If the folder does not exist, it will create a new folder with that name.
+</t>
   </si>
   <si>
     <t>output_folder</t>
@@ -100,15 +144,40 @@
     <t>GROUPING</t>
   </si>
   <si>
-    <t>Replicates per group:</t>
-  </si>
-  <si>
-    <t>Positive integer. 
-Example: 5</t>
-  </si>
-  <si>
-    <t>How many raw files belong to each sample/group. 
-For example, if each biological sample has 5 replicate files, use 5.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Replicates per group:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive integer. 
+Example: 3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+How many raw files belong to each sample/group.
+Note that the code assumes the replicates are saved consecutively.
+For example, if each sample has 3 replicate files, use 3.
+</t>
   </si>
   <si>
     <t>replicates_per_group</t>
@@ -117,11 +186,16 @@
     <t>Sample names:</t>
   </si>
   <si>
-    <t>List of group names, or None. 
-Example: ["Liver1", "Liver2"]</t>
-  </si>
-  <si>
-    <t>Optional group names. These names will be assigned to groups according to the detected file order. If you do not want to provide names, write None. Then groups will be named automatically: Group_1, Group_2, Group_3, ...</t>
+    <t xml:space="preserve">
+List of group names, or None. 
+Example: ["Liver", "Kidney", "Lung"]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Optional labels for each group of replicates. These names will be assigned to groups according to the detected file order.
+If you do not want to provide names, leave None. Then groups will be named automatically: Group_1, Group_2, Group_3, ...
+</t>
   </si>
   <si>
     <t>sample_tags</t>
@@ -133,10 +207,16 @@
     <t>False</t>
   </si>
   <si>
-    <t>True / False</t>
-  </si>
-  <si>
-    <t>What to do with leftover files that do not complete a full group. False = ignore leftover files and print a warning. True = analyse leftover files as an additional group named Extra.</t>
+    <t xml:space="preserve">
+True / False
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Handle the extra files that don't complete a full group of replicates: 
+•  False = ignore leftover files and print a message to the user.
+•  True = analyse leftover files as an additional group named Extra.
+</t>
   </si>
   <si>
     <t>include_extra_group</t>
@@ -148,11 +228,15 @@
     <t>Maximum background noise:</t>
   </si>
   <si>
-    <t>Number. 
-Example: 25</t>
-  </si>
-  <si>
-    <t>The minimum counts/sec value that marks the beginning of the real signal. All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.</t>
+    <t xml:space="preserve">
+Number. 
+Example: 25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The minimum counts/sec value that marks the beginning of the real signal.All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.
+</t>
   </si>
   <si>
     <t>noise_max</t>
@@ -164,7 +248,10 @@
     <t>True</t>
   </si>
   <si>
-    <t>True = subtract the average pre-sample noise from the signal. False = keep the signal without subtracting that background.</t>
+    <t xml:space="preserve">
+•  True = subtract the average pre-sample noise from the signal.
+•  False = keep the signal without subtracting that background.
+</t>
   </si>
   <si>
     <t>remove_noise</t>
@@ -179,10 +266,15 @@
     <t>.csv</t>
   </si>
   <si>
-    <t>File extension as text. Usually .csv</t>
-  </si>
-  <si>
-    <t>Usually this should not be changed. Change only if the Lumi output files use a different file extension.</t>
+    <t xml:space="preserve">
+File extension. 
+Example .csv
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. Change only if the Lumi output files use a different file extension.
+</t>
   </si>
   <si>
     <t>extension</t>
@@ -194,11 +286,15 @@
     <t>_Raw</t>
   </si>
   <si>
-    <t>Text suffix. 
-Example: _Raw</t>
-  </si>
-  <si>
-    <t>Usually this should not be changed. This suffix is removed from raw file names when creating cleaner names.</t>
+    <t xml:space="preserve">
+Text suffix. 
+Example: _Raw
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. This suffix is removed from raw file names when creating cleaner names.
+</t>
   </si>
   <si>
     <t>suffix_to_remove</t>
@@ -210,11 +306,15 @@
     <t>_Raw.csv</t>
   </si>
   <si>
-    <t>Text suffix. 
-Example: _Raw.csv</t>
-  </si>
-  <si>
-    <t>Usually this should not be changed. Change only if the Lumi output files use different names.</t>
+    <t xml:space="preserve">
+Text suffix. 
+Example: _Raw.csv
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. Change only if the Lumi output files use different names.
+</t>
   </si>
   <si>
     <t>file_suffix</t>
@@ -226,7 +326,10 @@
     <t>Save processed files:</t>
   </si>
   <si>
-    <t>True = save processed files to output_folder. False = run analysis without saving files.</t>
+    <t xml:space="preserve">
+•  True = save processed files to the given output folder.
+•  False = run analysis without saving files.
+</t>
   </si>
   <si>
     <t>save_file</t>
@@ -238,23 +341,33 @@
     <t>Length of Lumi's interval:</t>
   </si>
   <si>
-    <t>Positive number. 
-Example: 10</t>
-  </si>
-  <si>
-    <t>Sampling interval in minutes.</t>
+    <t xml:space="preserve">
+Positive number. 
+Example: 10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The length of the sampling interval in minutes. 
+Note: Lumi's interval by default is 10 minutes.
+</t>
   </si>
   <si>
     <t>interval_minutes</t>
   </si>
   <si>
-    <t>Maximum days:</t>
-  </si>
-  <si>
-    <t>Positive number, or None.</t>
-  </si>
-  <si>
-    <t>Optional: limit analysis to the first N days after alignment. Use only one of max_rows, max_hours, max_days. Leave all as None to keep the full data.</t>
+    <t>Maximum days to analyze:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive number, or None.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Limit analysis to the first N days. Leave None for no limit, or choose a positive number N for number of days to analyze.
+This feature is useful to cut the tail of the data if it isn't significant to the analysis.
+</t>
   </si>
   <si>
     <t>max_days</t>
@@ -266,7 +379,10 @@
     <t>Create plots of the data:</t>
   </si>
   <si>
-    <t>True = create and save raw-data plots. False = do not create raw-data plots.</t>
+    <t xml:space="preserve">
+•  True = create and save raw-data plots. 
+•  False = do not create raw-data plots.
+</t>
   </si>
   <si>
     <t>plot_raw_data</t>
@@ -275,10 +391,23 @@
     <t>Replicate display mode:</t>
   </si>
   <si>
-    <t>replicates_and_mean / mean_only / replicates_only</t>
-  </si>
-  <si>
-    <t>Choose what to display on the raw-data plots. replicates_and_mean = show both replicates and the average signal. mean_only = show only the average signal. replicates_only = show only the replicate signals, without the average.</t>
+    <t>replicates_and_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+replicates_and_mean /
+mean_only /
+replicates_only
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Choose what to display on the raw-data plots from these options:
+•  replicates_and_mean = show replicates and their average.
+•  mean_only = show only the average signal.
+•  replicates_only = show only the replicates, without the average.
+Note: you can also hide specific replicates in the override section.
+</t>
   </si>
   <si>
     <t>replicate_display_mode</t>
@@ -287,10 +416,22 @@
     <t>Choose plot style:</t>
   </si>
   <si>
-    <t>points / line / points+line</t>
-  </si>
-  <si>
-    <t>Plot display style. points = plot data as points only. line = plot data as continuous lines. points+line = plot points connected by lines.</t>
+    <t>line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+points /
+line /
+points+line
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Plot display style - choose from the options below:
+•  points = plot data as points only.
+•  line = plot data as continuous lines.
+•  points+line = plot points connected by lines.
+</t>
   </si>
   <si>
     <t>plot_style</t>
@@ -299,14 +440,18 @@
     <t>Y-axis upper limit:</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>None, a number, or a tuple. 
-Examples: None, 500, (-100, 500)</t>
-  </si>
-  <si>
-    <t>Y-axis limit. None = automatic y-axis scaling. 500 = y-axis from 0 to 500. (-100, 500) = y-axis from -100 to 500.</t>
+    <t xml:space="preserve">
+None, an upper limit, or a range. 
+Examples: None, 500, (-100, 500)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+You can choose a unified Y-axis limit for all the groups:
+•  None = automatic y-axis scaling.
+•  500 = y-axis from 0 to 500.
+•  (-100, 500) = y-axis from -100 to 500.
+</t>
   </si>
   <si>
     <t>y_limit</t>
@@ -315,10 +460,16 @@
     <t>Plot description:</t>
   </si>
   <si>
-    <t>Text, or None.</t>
-  </si>
-  <si>
-    <t>Optional text shown in the top-right corner of the plot. Use None for no description or write the desired text.</t>
+    <t xml:space="preserve">
+Text, or None. 
+Example: "Experiment 2.6.26".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Optional text shown in the top-right corner of the plot.
+Use None for no description or write the desired text in quotes " ".
+</t>
   </si>
   <si>
     <t>description</t>
@@ -327,12 +478,16 @@
     <t>CT start hour:</t>
   </si>
   <si>
-    <t>Number. 
-Example: 6</t>
-  </si>
-  <si>
-    <t>CT shift. This changes the CT values used in saved condensed data and plots. 
-Example: ct_start_hour = 6 means the first row is CT = 6.</t>
+    <t xml:space="preserve">
+Number. 
+Example: 6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+CT shift - this changes the CT values to start from the given shift.
+Example: CT start hour = 6 means the first row is CT = 6.
+</t>
   </si>
   <si>
     <t>ct_start_hour</t>
@@ -341,10 +496,16 @@
     <t>X-axis start (only changes the plot):</t>
   </si>
   <si>
-    <t>Number. Usually 0.</t>
-  </si>
-  <si>
-    <t>Left x-axis limit for plots. Usually keep 0 so the plot axis starts visually at 0, even if the first data point starts at shifted CT such as 6.</t>
+    <t xml:space="preserve">
+Number. 
+(Usually 0)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Left x-axis limit for the plots. 
+Usually keep 0 so the plot axis starts visually at 0, even if the first data point starts at some shifted CT such as 6.
+</t>
   </si>
   <si>
     <t>x_axis_start</t>
@@ -356,7 +517,10 @@
     <t>Show peaks:</t>
   </si>
   <si>
-    <t>True = detect and mark peaks on raw-data plots. False = do not show peaks.</t>
+    <t xml:space="preserve">
+•  True = show peaks for each replicate on raw-data plots. 
+•  False = do not show peaks for the replicates.
+</t>
   </si>
   <si>
     <t>plot_peaks</t>
@@ -365,7 +529,10 @@
     <t>Show average peaks:</t>
   </si>
   <si>
-    <t>Whether to show peak markers for the average signal.</t>
+    <t xml:space="preserve">
+•  True = show the peaks of the average signal on raw-data plots.
+•  False = do not show peaks for the average signal.
+</t>
   </si>
   <si>
     <t>show_average_peaks</t>
@@ -374,7 +541,10 @@
     <t>Show average peak labels:</t>
   </si>
   <si>
-    <t>Whether to show text labels next to average-signal peaks.</t>
+    <t xml:space="preserve">
+•  True = show text labels with CT next to average-signal peaks.
+•  False = do not show CT labels.
+</t>
   </si>
   <si>
     <t>show_average_peaks_txt</t>
@@ -386,7 +556,10 @@
     <t>Save peak/period tables:</t>
   </si>
   <si>
-    <t>True = create an Excel file with one peaks/periods table per group.</t>
+    <t xml:space="preserve">
+•  True = create an Excel file with peaks + periods table per group.
+•  False = do not create an Excel file for peaks + periods.
+</t>
   </si>
   <si>
     <t>save_peak_tables</t>
@@ -395,11 +568,15 @@
     <t>Peak table decimals:</t>
   </si>
   <si>
-    <t>Non-negative integer. 
-Example: 2</t>
-  </si>
-  <si>
-    <t>Number of decimals in peak and period values.</t>
+    <t xml:space="preserve">
+Non-negative integer. 
+Example: 2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Number of decimals in peak and period values.
+</t>
   </si>
   <si>
     <t>peak_table_decimals</t>
@@ -414,10 +591,22 @@
     <t>[]</t>
   </si>
   <si>
-    <t>List of group names. Example: ["Liver1", "Liver2", "Kid1"]</t>
-  </si>
-  <si>
-    <t>Use this section only when you want to override specific settings for specific groups. First, write the group names in this row as a list. Then, for each override setting below, write a list with the same number of positions and in the same order. Each position matches the group name in the same position. Leave an empty position when you do not want to override that setting for that group. For example, if group names are ["Liver1", "Liver2", "Kid1"], then [500, , 700] means: Liver1 gets 500, Liver2 gets no override, and Kid1 gets 700. Spaces in empty positions are allowed. For text values, use quotes, for example: ["Control", , "Kidney"].</t>
+    <t xml:space="preserve">
+List of group names. 
+Example: ["Liver", "Kidney", "Lung"]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Use this section only when you want to override specific settings for specific groups.
+First, write the group names in this row as a list. List only the groups for which you'd like to adjust the settings.
+Then, for each override setting below, write a list with the same number of positions and in the same order.
+Each position matches the group name in the same position.
+Leave an empty position when you do not want to override that setting for that group.
+For example, if group names are ["Liver", "Kidney", "Lung"], then [500, , 700] means:
+Liver gets 500, Kidney gets no override, and Lung gets 700.
+Spaces in empty positions are allowed. For text values, use quotes, for example: ["Control", , "Kidney"].
+</t>
   </si>
   <si>
     <t>override_group_names</t>
@@ -426,19 +615,29 @@
     <t>Y-axis limit:</t>
   </si>
   <si>
-    <t>List with one value per group, or an empty position for no override. Example: [500, , (-100, 500)]</t>
-  </si>
-  <si>
-    <t>See section: PLOTTING SETTINGS, setting: Y-axis limit, for a detailed description.</t>
+    <t xml:space="preserve">
+List with one value per group, or an empty position for no override. 
+Example: [500, , (-100, 500)]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+See section: PLOTTING SETTINGS, setting: Y-axis limit, for a detailed description.
+</t>
   </si>
   <si>
     <t>override_y_limit</t>
   </si>
   <si>
-    <t>List with one value per group, or an empty position for no override. Example: ["Control", , "Kidney"]</t>
-  </si>
-  <si>
-    <t>See section: PLOTTING SETTINGS, setting: Plot description, for a detailed description.</t>
+    <t xml:space="preserve">
+List with one value per group, or an empty position for no override. 
+Example: ["Control", , "Kidney"]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+See section: PLOTTING SETTINGS, setting: Plot description, for a detailed description.
+</t>
   </si>
   <si>
     <t>override_description</t>
@@ -447,10 +646,15 @@
     <t>Peak label vertical offset:</t>
   </si>
   <si>
-    <t>List with one value per group, or an empty position for no override. Example: [20, , 35]</t>
-  </si>
-  <si>
-    <t>See section: PEAK SETTINGS, setting: Peak label vertical offset, for a detailed description.</t>
+    <t xml:space="preserve">
+List with one value per group, or an empty position for no override. 
+Example: [20, , 35]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+This value is used to adjust the position of the peak text labels.
+</t>
   </si>
   <si>
     <t>override_peak_txt_dy</t>
@@ -459,10 +663,16 @@
     <t>Replicates to disable:</t>
   </si>
   <si>
-    <t>List with one value per group, or an empty position for no override. Example: [None, ["c i", "c iii"], ]</t>
-  </si>
-  <si>
-    <t>See section: PLOTTING SETTINGS, setting: Replicates used for mean, for a detailed description.</t>
+    <t xml:space="preserve">
+List with one value per group, or an empty position for no override.
+Each value has to be a list [] of replicates names in quotes, or None.
+Example: [None, ["1a", "1b"], ]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+For each group choose specific replicates to disable from the average signal.
+</t>
   </si>
   <si>
     <t>override_mean_replicate_cols</t>
@@ -471,39 +681,24 @@
     <t>Replicates to hide:</t>
   </si>
   <si>
-    <t>List with one value per group, or an empty position for no override. Example: [None, [], ["c i"]]</t>
-  </si>
-  <si>
-    <t>See section: PLOTTING SETTINGS, setting: Replicates shown on plot, for a detailed description.</t>
+    <t xml:space="preserve">
+For each group choose specific replicates to hide from the plot.
+Note: this does NOT disable them from the calculation of the average signal.
+</t>
   </si>
   <si>
     <t>override_visible_replicate_cols</t>
-  </si>
-  <si>
-    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM2/Analysis/</t>
-  </si>
-  <si>
-    <t>["10% serum", "2% serum", "20% serum", "Dex - 10% serum", "Allicin 1", "Allicin 10", "Allicin 25", "Allicin 10 (26.3)", "Allicin 25 (26.3)"]</t>
-  </si>
-  <si>
-    <t>points+line</t>
-  </si>
-  <si>
-    <t>"DM2"</t>
-  </si>
-  <si>
-    <t>mean_only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -511,7 +706,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -519,7 +714,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -527,14 +722,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -542,7 +737,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -612,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,6 +818,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -641,33 +839,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -705,7 +889,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -739,7 +923,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -774,10 +957,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -950,17 +1132,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="4" width="42.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="78.7109375" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -980,706 +1162,717 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:6" ht="20" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="6" spans="1:6" ht="20" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="96" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="10" spans="1:6" ht="20" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="8">
-        <v>20</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="9">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="13" spans="1:6" ht="20" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="17" spans="1:6" ht="20" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="19" spans="1:6" ht="20" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <v>10</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="6" t="s">
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="20" customHeight="1">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="20" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="E35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="9">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="20" customHeight="1">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="37.200000000000003" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="204.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="55.8" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="D40" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="E40" s="6" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="7" t="s">
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="C41" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="E41" s="6" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="5" t="s">
+      <c r="F41" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="7" t="s">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="C42" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="5" t="s">
+      <c r="F42" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="7" t="s">
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="C43" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="6" t="s">
         <v>140</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:A29"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
       <formula1>"points,line,points+line"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46299D3B-DA6B-4567-9774-E8ED6FE8EB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="8340" yWindow="108" windowWidth="14700" windowHeight="12132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="144">
   <si>
     <t>Section</t>
   </si>
@@ -65,7 +71,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -75,7 +81,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -105,7 +111,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -115,7 +121,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -123,9 +129,6 @@
     </r>
   </si>
   <si>
-    <t>analysis_output</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Folder name 
 or 
@@ -149,7 +152,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -159,7 +162,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -689,16 +692,28 @@
   <si>
     <t>override_visible_replicate_cols</t>
   </si>
+  <si>
+    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM3/Analysis/</t>
+  </si>
+  <si>
+    <t>DM3 Analysis</t>
+  </si>
+  <si>
+    <t>["25", "c", "dex 25", "dex"]</t>
+  </si>
+  <si>
+    <t>"DM3 Analysis"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -706,7 +721,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -714,7 +729,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -722,14 +737,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -737,7 +752,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -746,6 +761,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -807,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -818,9 +841,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -839,19 +859,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -889,7 +923,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -923,6 +957,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -957,9 +992,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1132,17 +1168,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="78.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.69921875" customWidth="1"/>
+    <col min="2" max="4" width="42.69921875" customWidth="1"/>
+    <col min="5" max="5" width="78.69921875" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,717 +1198,706 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="8">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9">
-        <v>3</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="6" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="8">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9">
-        <v>25</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="6" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="8">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="9">
-        <v>10</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6">
+        <v>7</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="20" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="6" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="6" t="s">
+    </row>
+    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="6">
+        <v>8500</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="6" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="6" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="9">
+      <c r="E28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="6" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="F31" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="F32" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="F33" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="20" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="6" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="9">
-        <v>2</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="6" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="316.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="20" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="D38" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="6" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="5" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="E39" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F39" s="6" t="s">
+    </row>
+    <row r="40" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="8" t="s">
+      <c r="E40" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="6" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" s="8" t="s">
+      <c r="E41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="6" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="8" t="s">
+      <c r="E42" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F42" s="6" t="s">
+    </row>
+    <row r="43" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
-      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46299D3B-DA6B-4567-9774-E8ED6FE8EB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBAEB9F-C59D-4E09-9FD0-33E0A9A017A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="108" windowWidth="14700" windowHeight="12132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-Paste the path to the folder that contains the Lumi raw CSV files. The folder should contain files such as 1a_Raw.csv, 1b_Raw.csv, 2a_Raw.csv, etc.Make sure the backslashes / are in the same direction as here.
+Paste the path to the folder that contains the Lumi raw CSV files. The folder should contain files such as 1a_Raw.csv, 1b_Raw.csv, 2a_Raw.csv, etc.
 </t>
   </si>
   <si>
@@ -1206,7 +1206,7 @@
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>16</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>64</v>
       </c>
       <c r="C21" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>65</v>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBAEB9F-C59D-4E09-9FD0-33E0A9A017A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="141">
   <si>
     <t>Section</t>
   </si>
@@ -71,7 +65,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +75,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -111,7 +105,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -121,7 +115,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -129,6 +123,9 @@
     </r>
   </si>
   <si>
+    <t>analysis_output</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Folder name 
 or 
@@ -152,7 +149,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -162,7 +159,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -692,28 +689,16 @@
   <si>
     <t>override_visible_replicate_cols</t>
   </si>
-  <si>
-    <t>C:/Users/yuval/OneDrive/Desktop/Lumi/DM3/Analysis/</t>
-  </si>
-  <si>
-    <t>DM3 Analysis</t>
-  </si>
-  <si>
-    <t>["25", "c", "dex 25", "dex"]</t>
-  </si>
-  <si>
-    <t>"DM3 Analysis"</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -721,7 +706,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -729,7 +714,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -737,14 +722,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -752,7 +737,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -761,14 +746,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -830,7 +807,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -841,6 +818,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -859,33 +839,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -923,7 +889,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -957,7 +923,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -992,10 +957,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1168,17 +1132,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="4" width="42.69921875" customWidth="1"/>
-    <col min="5" max="5" width="78.69921875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="78.7109375" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,706 +1162,717 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:6" ht="20" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="9">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="9">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="20" customHeight="1">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="20" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="9">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="20" customHeight="1">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="8">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="8">
-        <v>25</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="8">
-        <v>10</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="6">
-        <v>9</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="6">
-        <v>8500</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="316.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:A29"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
       <formula1>"points,line,points+line"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466F94C8-7F56-413A-8ABB-D987D060B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1152" yWindow="108" windowWidth="14700" windowHeight="12132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="147">
   <si>
     <t>Section</t>
   </si>
@@ -65,7 +71,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -75,7 +81,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -105,7 +111,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -115,7 +121,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -123,9 +129,6 @@
     </r>
   </si>
   <si>
-    <t>analysis_output</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 Folder name 
 or 
@@ -149,7 +152,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -159,7 +162,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -689,16 +692,37 @@
   <si>
     <t>override_visible_replicate_cols</t>
   </si>
+  <si>
+    <t>C:\Users\yuval\OneDrive\Desktop\Lumi\ORG slices contr females 13.4.26\Analysis</t>
+  </si>
+  <si>
+    <t>["Liver1", "Liver2", "Kid1", "Kid2", "Lung1", "Lung2"]</t>
+  </si>
+  <si>
+    <t>Control (F) 13.04.2026</t>
+  </si>
+  <si>
+    <t>["Kid1", "Kid2", "Liver1", "Liver2", "Lung1", "Lung2"]</t>
+  </si>
+  <si>
+    <t>[250, 250, 200, 200, 400, 600]</t>
+  </si>
+  <si>
+    <t>Control (F) - Override Test</t>
+  </si>
+  <si>
+    <t>[None ,None , ["2a"], ["2c"], None, ["7c"]]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -706,7 +730,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -714,7 +738,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -722,14 +746,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -737,7 +761,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -746,6 +770,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -807,7 +839,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -818,9 +850,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -839,19 +868,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -889,7 +932,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -923,6 +966,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -957,9 +1001,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1132,17 +1177,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="78.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.69921875" customWidth="1"/>
+    <col min="2" max="4" width="42.69921875" customWidth="1"/>
+    <col min="5" max="5" width="78.69921875" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,717 +1207,702 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="8">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9">
-        <v>3</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="6" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="8">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9">
-        <v>25</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="6" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="8">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="9">
-        <v>10</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8" t="s">
+      <c r="E21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="20" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="6" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="6" t="s">
+    </row>
+    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="E25" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="6" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="s">
+      <c r="E27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="6" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="8">
+        <v>6</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="9">
+      <c r="E28" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="6" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="F31" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="F32" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="F33" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="20" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="6" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="9">
-        <v>2</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="6" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="316.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="20" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
+      <c r="B38" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F39" s="6" t="s">
+      <c r="D40" s="7" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="8" t="s">
+      <c r="E40" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="6" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" s="8" t="s">
+      <c r="E41" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="6" t="s">
+    </row>
+    <row r="42" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="8" t="s">
+      <c r="E42" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F42" s="6" t="s">
+    </row>
+    <row r="43" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
-      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466F94C8-7F56-413A-8ABB-D987D060B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="108" windowWidth="14700" windowHeight="12132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
   <si>
     <t>Section</t>
   </si>
@@ -71,7 +65,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +75,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -111,7 +105,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -121,7 +115,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -129,6 +123,9 @@
     </r>
   </si>
   <si>
+    <t>analysis_output</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Folder name 
 or 
@@ -152,7 +149,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -162,7 +159,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -602,10 +599,10 @@
   <si>
     <t xml:space="preserve">
 Use this section only when you want to override specific settings for specific groups.
-First, write the group names in this row as a list. List only the groups for which you'd like to adjust the settings.
-Then, for each override setting below, write a list with the same number of positions and in the same order.
-Each position matches the group name in the same position.
-Leave an empty position when you do not want to override that setting for that group.
+Important Notes:
+NOTE #1: write only the groups for which you want to override at least one setting.
+NOTE #2: each group name MUST be in quotes (example: "Liver").
+NOTE #3: when overriding a setting, maintain the same order in which you listed the groups.Each position matches the group name in the same position.
 For example, if group names are ["Liver", "Kidney", "Lung"], then [500, , 700] means:
 Liver gets 500, Kidney gets no override, and Lung gets 700.
 Spaces in empty positions are allowed. For text values, use quotes, for example: ["Control", , "Kidney"].
@@ -619,8 +616,8 @@
   </si>
   <si>
     <t xml:space="preserve">
-List with one value per group, or an empty position for no override. 
-Example: [500, , (-100, 500)]
+List with one value (number/range) per group, or None for no override.
+Example: [500, None, (-100, 500)]
 </t>
   </si>
   <si>
@@ -633,8 +630,8 @@
   </si>
   <si>
     <t xml:space="preserve">
-List with one value per group, or an empty position for no override. 
-Example: ["Control", , "Kidney"]
+List with one value per group, or None for no override. 
+Example: ["Exp. 1", None, None, None]
 </t>
   </si>
   <si>
@@ -650,8 +647,8 @@
   </si>
   <si>
     <t xml:space="preserve">
-List with one value per group, or an empty position for no override. 
-Example: [20, , 35]
+List with one value per group, or None for no override. 
+Example: [20, None, None, 35]
 </t>
   </si>
   <si>
@@ -667,14 +664,21 @@
   </si>
   <si>
     <t xml:space="preserve">
-List with one value per group, or an empty position for no override.
-Each value has to be a list [] of replicates names in quotes, or None.
-Example: [None, ["1a", "1b"], ]
+Examples:
+• Single replicate:
+[None, None, ["2a"], None]
+• Multiple replicates:
+[None, ["1a", "1b"], ["2c"], None]
+• INCORRECT:
+[None, None, "2a", None]
 </t>
   </si>
   <si>
     <t xml:space="preserve">
 For each group choose specific replicates to disable from the average signal.
+NOTE #1: each value in the outer list has to be either a list or None.
+NOTE #2: each replicate has to be written inside quotes (" ").
+NOTE #3: disabling a replicate also removes it from the plot.
 </t>
   </si>
   <si>
@@ -685,44 +689,28 @@
   </si>
   <si>
     <t xml:space="preserve">
+See examples above.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 For each group choose specific replicates to hide from the plot.
-Note: this does NOT disable them from the calculation of the average signal.
+NOTE: this does NOT exclude them from the calculation of the average signal.
 </t>
   </si>
   <si>
     <t>override_visible_replicate_cols</t>
-  </si>
-  <si>
-    <t>C:\Users\yuval\OneDrive\Desktop\Lumi\ORG slices contr females 13.4.26\Analysis</t>
-  </si>
-  <si>
-    <t>["Liver1", "Liver2", "Kid1", "Kid2", "Lung1", "Lung2"]</t>
-  </si>
-  <si>
-    <t>Control (F) 13.04.2026</t>
-  </si>
-  <si>
-    <t>["Kid1", "Kid2", "Liver1", "Liver2", "Lung1", "Lung2"]</t>
-  </si>
-  <si>
-    <t>[250, 250, 200, 200, 400, 600]</t>
-  </si>
-  <si>
-    <t>Control (F) - Override Test</t>
-  </si>
-  <si>
-    <t>[None ,None , ["2a"], ["2c"], None, ["7c"]]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -730,7 +718,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -738,7 +726,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -746,14 +734,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -761,7 +749,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -770,14 +758,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -839,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -850,6 +830,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -868,33 +851,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -932,7 +901,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -966,7 +935,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1001,10 +969,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1177,17 +1144,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="4" width="42.69921875" customWidth="1"/>
-    <col min="5" max="5" width="78.69921875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="78.7109375" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,702 +1174,717 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:6" ht="20" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="20" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="9">
+        <v>25</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="9">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="20" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="20" customHeight="1">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="20" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="9">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="20" customHeight="1">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="8">
-        <v>5</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="8">
-        <v>25</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="8">
-        <v>10</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="8">
-        <v>6</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="316.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:A29"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
       <formula1>"points,line,points+line"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,25 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F909DF0E-F515-4D3B-A2FE-AC2D7409674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="143">
   <si>
     <t>Section</t>
   </si>
@@ -65,7 +71,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -75,7 +81,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -105,7 +111,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -115,7 +121,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -149,7 +155,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -159,7 +165,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -603,9 +609,8 @@
 NOTE #1: write only the groups for which you want to override at least one setting.
 NOTE #2: each group name MUST be in quotes (example: "Liver").
 NOTE #3: when overriding a setting, maintain the same order in which you listed the groups.Each position matches the group name in the same position.
-For example, if group names are ["Liver", "Kidney", "Lung"], then [500, , 700] means:
+For example, if group names are ["Liver", "Kidney", "Lung"], then [500, None, 700] means:
 Liver gets 500, Kidney gets no override, and Lung gets 700.
-Spaces in empty positions are allowed. For text values, use quotes, for example: ["Control", , "Kidney"].
 </t>
   </si>
   <si>
@@ -701,16 +706,19 @@
   <si>
     <t>override_visible_replicate_cols</t>
   </si>
+  <si>
+    <t>C:\Users\yuval\OneDrive\Desktop\Lumi\Lumi files</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -718,7 +726,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -726,7 +734,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -734,14 +742,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -749,7 +757,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -758,6 +766,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -819,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -830,9 +846,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -851,19 +864,33 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -901,7 +928,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -935,6 +962,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -969,9 +997,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1144,17 +1173,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="78.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.69921875" customWidth="1"/>
+    <col min="2" max="4" width="42.69921875" customWidth="1"/>
+    <col min="5" max="5" width="78.69921875" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1174,717 +1203,698 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>3</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>25</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>10</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
+    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
+    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6" t="s">
+    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
+    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="6"/>
+      <c r="D26" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
+    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="s">
+      <c r="C27" s="6"/>
+      <c r="D27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
+    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>0</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
+    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <v>0</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
+    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6" t="s">
+    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
+    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="20" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
+    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6" t="s">
+    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>2</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="20" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
+    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+    </row>
+    <row r="38" spans="1:6" ht="297.60000000000002" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6" t="s">
+    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
+    <row r="40" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
+    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
+    <row r="42" spans="1:6" ht="223.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
+    <row r="43" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>141</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
-      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuval\PycharmProjects\Lumi Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F909DF0E-F515-4D3B-A2FE-AC2D7409674D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
   <si>
     <t>Section</t>
   </si>
@@ -71,7 +65,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -81,7 +75,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -111,7 +105,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -121,7 +115,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -155,7 +149,7 @@
         <b/>
         <sz val="20"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -165,7 +159,7 @@
       <rPr>
         <sz val="15"/>
         <color theme="1"/>
-        <rFont val="Arial"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -200,7 +194,7 @@
   <si>
     <t xml:space="preserve">
 Optional labels for each group of replicates. These names will be assigned to groups according to the detected file order.
-If you do not want to provide names, leave None. Then groups will be named automatically: Group_1, Group_2, Group_3, ...
+If no labels are provided, the groups will be named automatically: "Unlabeled_1", "Unlabeled_2", "Unlabeled_3", ...
 </t>
   </si>
   <si>
@@ -355,7 +349,7 @@
   <si>
     <t xml:space="preserve">
 The length of the sampling interval in minutes. 
-Note: Lumi's interval by default is 10 minutes.
+NOTE: Lumi's interval by default is 10 minutes.
 </t>
   </si>
   <si>
@@ -412,7 +406,7 @@
 •  replicates_and_mean = show replicates and their average.
 •  mean_only = show only the average signal.
 •  replicates_only = show only the replicates, without the average.
-Note: you can also hide specific replicates in the override section.
+NOTE: you can also hide specific replicates in the override section.
 </t>
   </si>
   <si>
@@ -706,19 +700,16 @@
   <si>
     <t>override_visible_replicate_cols</t>
   </si>
-  <si>
-    <t>C:\Users\yuval\OneDrive\Desktop\Lumi\Lumi files</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -726,7 +717,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -734,7 +725,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -742,14 +733,14 @@
       <b/>
       <sz val="15"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -757,7 +748,7 @@
       <b/>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -766,14 +757,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -835,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -846,6 +829,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -864,33 +850,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -928,7 +900,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -962,7 +934,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -997,10 +968,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1173,17 +1143,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" customWidth="1"/>
-    <col min="2" max="4" width="42.69921875" customWidth="1"/>
-    <col min="5" max="5" width="78.69921875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="78.7109375" customWidth="1"/>
     <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,698 +1173,717 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="2" spans="1:6" ht="20" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="6" spans="1:6" ht="20" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>3</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="10" spans="1:6" ht="20" customHeight="1">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>25</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="13" spans="1:6" ht="20" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:6">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="17" spans="1:6" ht="20" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+    <row r="19" spans="1:6" ht="20" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <v>10</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="22" spans="1:6" ht="20" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="167.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="5" t="s">
+    <row r="26" spans="1:6">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="1:6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="9">
         <v>0</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="5" t="s">
+    <row r="29" spans="1:6">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="9">
         <v>0</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+    <row r="30" spans="1:6" ht="20" customHeight="1">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="5" t="s">
+    <row r="32" spans="1:6">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="5" t="s">
+    <row r="33" spans="1:6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6" ht="74.400000000000006" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+    <row r="34" spans="1:6" ht="20" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="93" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="5" t="s">
+    <row r="36" spans="1:6">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="9">
         <v>2</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6" ht="297.60000000000002" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+    <row r="37" spans="1:6" ht="20" customHeight="1">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="5" t="s">
+    <row r="39" spans="1:6">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="130.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
+    <row r="40" spans="1:6">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="5" t="s">
+    <row r="41" spans="1:6">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="223.2" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="5" t="s">
+    <row r="42" spans="1:6">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="111.6" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="5" t="s">
+    <row r="43" spans="1:6">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="6" t="s">
         <v>141</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:A29"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9 C35 C31:C33 C23 C18 C12" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
       <formula1>"points,line,points+line"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -201,6 +201,31 @@
     <t>sample_tags</t>
   </si>
   <si>
+    <t>Disabled replicates:</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+List of replicate names. 
+Example: ["1a", "2b", "3c"]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Choose specific replicates to disable from the analysis.
+Disabled replicates are excluded from the analysis by replicate name.
+NOTE #1: each replicate name must be written inside quotes (" ").
+NOTE #2: write replicate names without suffixes.
+Correct example: ["1a", "2b"]
+Incorrect example: ["1a_Raw.csv", "2b_Raw.csv"]
+</t>
+  </si>
+  <si>
+    <t>disabled_replicates</t>
+  </si>
+  <si>
     <t>Include all files:</t>
   </si>
   <si>
@@ -586,9 +611,6 @@
   </si>
   <si>
     <t>Group names:</t>
-  </si>
-  <si>
-    <t>[]</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -657,31 +679,6 @@
   </si>
   <si>
     <t>override_peak_txt_dy</t>
-  </si>
-  <si>
-    <t>Replicates to disable:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Examples:
-• Single replicate:
-[None, None, ["2a"], None]
-• Multiple replicates:
-[None, ["1a", "1b"], ["2c"], None]
-• INCORRECT:
-[None, None, "2a", None]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-For each group choose specific replicates to disable from the average signal.
-NOTE #1: each value in the outer list has to be either a list or None.
-NOTE #2: each replicate has to be written inside quotes (" ").
-NOTE #3: disabling a replicate also removes it from the plot.
-</t>
-  </si>
-  <si>
-    <t>override_mean_replicate_cols</t>
   </si>
   <si>
     <t>Replicates to hide:</t>
@@ -1289,82 +1286,82 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9">
+      <c r="D10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="20" customHeight="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="9">
         <v>25</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="6" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="20" customHeight="1">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
         <v>46</v>
       </c>
@@ -1399,116 +1396,116 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+    <row r="17" spans="1:6">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="6" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="20" customHeight="1">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="9">
+      <c r="B19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20" customHeight="1">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="9">
         <v>10</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="7"/>
       <c r="D21" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="20" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="6" t="s">
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="F22" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20" customHeight="1">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="5"/>
+      <c r="A24" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="B24" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>76</v>
@@ -1540,214 +1537,214 @@
       <c r="B26" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="7"/>
+      <c r="C26" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="D26" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="9">
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="9">
         <v>0</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="20" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="6" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="E30" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="F30" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="20" customHeight="1">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="5"/>
+      <c r="A32" s="5" t="s">
+        <v>104</v>
+      </c>
       <c r="B32" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="20" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="6" t="s">
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="C34" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="F34" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="20" customHeight="1">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="5"/>
+      <c r="A36" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="B36" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="9">
+        <v>115</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="9">
         <v>2</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="20" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="D37" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="E37" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F38" s="6" t="s">
+    </row>
+    <row r="38" spans="1:6" ht="20" customHeight="1">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
         <v>123</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>124</v>
@@ -1762,28 +1759,28 @@
     <row r="40" spans="1:6">
       <c r="A40" s="5"/>
       <c r="B40" s="6" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>131</v>
@@ -1801,7 +1798,7 @@
         <v>134</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>135</v>
@@ -1819,7 +1816,7 @@
         <v>138</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>139</v>
@@ -1837,44 +1834,41 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A39:A43"/>
   </mergeCells>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C10">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C13">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C18">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C19">
       <formula1>"True,False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
       <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C26">
       <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
-      <formula1>"True,False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
       <formula1>"True,False"</formula1>
@@ -1882,7 +1876,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C34">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C36">
       <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -226,7 +226,7 @@
     <t>disabled_replicates</t>
   </si>
   <si>
-    <t>Include all files:</t>
+    <t>Include extra files:</t>
   </si>
   <si>
     <t>False</t>
@@ -247,161 +247,13 @@
     <t>include_extra_group</t>
   </si>
   <si>
-    <t>ANALYSIS SETTINGS</t>
-  </si>
-  <si>
-    <t>Maximum background noise:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Number. 
-Example: 25
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The minimum counts/sec value that marks the beginning of the real signal.All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.
-</t>
-  </si>
-  <si>
-    <t>noise_max</t>
-  </si>
-  <si>
-    <t>Remove background noise:</t>
+    <t>PLOTTING SETTINGS</t>
+  </si>
+  <si>
+    <t>Create plots of the data:</t>
   </si>
   <si>
     <t>True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-•  True = subtract the average pre-sample noise from the signal.
-•  False = keep the signal without subtracting that background.
-</t>
-  </si>
-  <si>
-    <t>remove_noise</t>
-  </si>
-  <si>
-    <t>FILE SETTINGS</t>
-  </si>
-  <si>
-    <t>File extension:</t>
-  </si>
-  <si>
-    <t>.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-File extension. 
-Example .csv
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. Change only if the Lumi output files use a different file extension.
-</t>
-  </si>
-  <si>
-    <t>extension</t>
-  </si>
-  <si>
-    <t>Suffix to remove:</t>
-  </si>
-  <si>
-    <t>_Raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Text suffix. 
-Example: _Raw
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. This suffix is removed from raw file names when creating cleaner names.
-</t>
-  </si>
-  <si>
-    <t>suffix_to_remove</t>
-  </si>
-  <si>
-    <t>Raw file suffix:</t>
-  </si>
-  <si>
-    <t>_Raw.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Text suffix. 
-Example: _Raw.csv
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. Change only if the Lumi output files use different names.
-</t>
-  </si>
-  <si>
-    <t>file_suffix</t>
-  </si>
-  <si>
-    <t>SAVING</t>
-  </si>
-  <si>
-    <t>Save processed files:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-•  True = save processed files to the given output folder.
-•  False = run analysis without saving files.
-</t>
-  </si>
-  <si>
-    <t>save_file</t>
-  </si>
-  <si>
-    <t>DATA LENGTH / TAIL CUTTING</t>
-  </si>
-  <si>
-    <t>Length of Lumi's interval:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Positive number. 
-Example: 10
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The length of the sampling interval in minutes. 
-NOTE: Lumi's interval by default is 10 minutes.
-</t>
-  </si>
-  <si>
-    <t>interval_minutes</t>
-  </si>
-  <si>
-    <t>Maximum days to analyze:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Positive number, or None.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Limit analysis to the first N days. Leave None for no limit, or choose a positive number N for number of days to analyze.
-This feature is useful to cut the tail of the data if it isn't significant to the analysis.
-</t>
-  </si>
-  <si>
-    <t>max_days</t>
-  </si>
-  <si>
-    <t>PLOTTING SETTINGS</t>
-  </si>
-  <si>
-    <t>Create plots of the data:</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -605,6 +457,154 @@
   </si>
   <si>
     <t>peak_table_decimals</t>
+  </si>
+  <si>
+    <t>DATA LENGTH / TAIL CUTTING</t>
+  </si>
+  <si>
+    <t>Length of Lumi's interval:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive number. 
+Example: 10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The length of the sampling interval in minutes. 
+NOTE: Lumi's interval by default is 10 minutes.
+</t>
+  </si>
+  <si>
+    <t>interval_minutes</t>
+  </si>
+  <si>
+    <t>Maximum days to analyze:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive number, or None.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Limit analysis to the first N days. Leave None for no limit, or choose a positive number N for number of days to analyze.
+This feature is useful to cut the tail of the data if it isn't significant to the analysis.
+</t>
+  </si>
+  <si>
+    <t>max_days</t>
+  </si>
+  <si>
+    <t>ANALYSIS SETTINGS</t>
+  </si>
+  <si>
+    <t>Maximum background noise:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Number. 
+Example: 25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The minimum counts/sec value that marks the beginning of the real signal.All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.
+</t>
+  </si>
+  <si>
+    <t>noise_max</t>
+  </si>
+  <si>
+    <t>Remove background noise:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+•  True = subtract the average pre-sample noise from the signal.
+•  False = keep the signal without subtracting that background.
+</t>
+  </si>
+  <si>
+    <t>remove_noise</t>
+  </si>
+  <si>
+    <t>FILE SETTINGS</t>
+  </si>
+  <si>
+    <t>File extension:</t>
+  </si>
+  <si>
+    <t>.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+File extension. 
+Example .csv
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. Change only if the Lumi output files use a different file extension.
+</t>
+  </si>
+  <si>
+    <t>extension</t>
+  </si>
+  <si>
+    <t>Suffix to remove:</t>
+  </si>
+  <si>
+    <t>_Raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Text suffix. 
+Example: _Raw
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. This suffix is removed from raw file names when creating cleaner names.
+</t>
+  </si>
+  <si>
+    <t>suffix_to_remove</t>
+  </si>
+  <si>
+    <t>Raw file suffix:</t>
+  </si>
+  <si>
+    <t>_Raw.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Text suffix. 
+Example: _Raw.csv
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Usually this should not be changed. Change only if the Lumi output files use different names.
+</t>
+  </si>
+  <si>
+    <t>file_suffix</t>
+  </si>
+  <si>
+    <t>SAVING</t>
+  </si>
+  <si>
+    <t>Save processed files:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+•  True = save processed files to the given output folder.
+•  False = run analysis without saving files.
+</t>
+  </si>
+  <si>
+    <t>save_file</t>
   </si>
   <si>
     <t>GROUP-SPECIFIC OVERRIDES</t>
@@ -1319,11 +1319,11 @@
       <c r="B12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="9">
-        <v>25</v>
+      <c r="C12" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>39</v>
@@ -1341,149 +1341,163 @@
         <v>42</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="20" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C15" s="7"/>
       <c r="D15" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C16" s="7"/>
       <c r="D16" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="20" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="8" t="s">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="20" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="9">
-        <v>10</v>
+        <v>71</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="7"/>
+        <v>74</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="D22" s="8" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="20" customHeight="1">
@@ -1496,230 +1510,216 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="C25" s="9">
+        <v>2</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="8" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="20" customHeight="1">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="6" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="B30" s="6" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6" t="s">
+      <c r="C30" s="9">
+        <v>25</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="9">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="6" t="s">
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
+      <c r="C31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="9">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="F31" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="6" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="20" customHeight="1">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="20" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="D33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="F34" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="20" customHeight="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="20" customHeight="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="9">
-        <v>2</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>119</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>120</v>
@@ -1777,7 +1777,7 @@
     <row r="41" spans="1:6">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>27</v>
@@ -1836,18 +1836,18 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A39:A43"/>
   </mergeCells>
@@ -1855,31 +1855,31 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C10">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C12">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C13">
+      <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C14">
+      <formula1>"points,line,points+line"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C20">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C21">
+      <formula1>"True,False"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C22">
       <formula1>"True,False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C25">
-      <formula1>"replicates_and_mean,mean_only,replicates_only"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C26">
-      <formula1>"points,line,points+line"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C34">
-      <formula1>"True,False"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C37">
       <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>Section</t>
   </si>
@@ -175,8 +175,8 @@
   <si>
     <t xml:space="preserve">
 How many raw files belong to each sample/group.
-Note that the code assumes the replicates are saved consecutively.
-For example, if each sample has 3 replicate files, use 3.
+They are grouped by their order in your folder.
+For example, if each sample has 4 replicate files, use 4.
 </t>
   </si>
   <si>
@@ -194,7 +194,6 @@
   <si>
     <t xml:space="preserve">
 Optional labels for each group of replicates. These names will be assigned to groups according to the detected file order.
-If no labels are provided, the groups will be named automatically: "Unlabeled_1", "Unlabeled_2", "Unlabeled_3", ...
 </t>
   </si>
   <si>
@@ -215,7 +214,6 @@
   <si>
     <t xml:space="preserve">
 Choose specific replicates to disable from the analysis.
-Disabled replicates are excluded from the analysis by replicate name.
 NOTE #1: each replicate name must be written inside quotes (" ").
 NOTE #2: write replicate names without suffixes.
 Correct example: ["1a", "2b"]
@@ -238,7 +236,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-Handle the extra files that don't complete a full group of replicates: 
+Handle the extra files that don't complete a full group: 
 •  False = ignore leftover files and print a message to the user.
 •  True = analyse leftover files as an additional group named Extra.
 </t>
@@ -427,6 +425,45 @@
     <t>show_average_peaks_txt</t>
   </si>
   <si>
+    <t>GROUP-SPECIFIC OVERRIDES</t>
+  </si>
+  <si>
+    <t>Group names:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+List of group names. 
+Example: ["Liver", "Lung"]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Use this section only when you want to limit Y-axis differently for specific groups.
+For example, if group names are ["Liver", "Lung"], then [500, 700] means:Liver gets 500, and Lung gets 700.
+NOTE: each group name MUST be in quotes (example: "Liver").Each position matches the group name in the same position.
+</t>
+  </si>
+  <si>
+    <t>override_group_names</t>
+  </si>
+  <si>
+    <t>Y-axis limit:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+List with limits (number/range).
+Example: [500, (-100, 500)]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+When choosing a limit, maintain the same order in which you listed the groups.
+</t>
+  </si>
+  <si>
+    <t>override_y_limit</t>
+  </si>
+  <si>
     <t>PEAK/PERIOD TABLE SETTINGS</t>
   </si>
   <si>
@@ -442,23 +479,6 @@
     <t>save_peak_tables</t>
   </si>
   <si>
-    <t>Peak table decimals:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Non-negative integer. 
-Example: 2
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Number of decimals in peak and period values.
-</t>
-  </si>
-  <si>
-    <t>peak_table_decimals</t>
-  </si>
-  <si>
     <t>DATA LENGTH / TAIL CUTTING</t>
   </si>
   <si>
@@ -529,69 +549,6 @@
     <t>remove_noise</t>
   </si>
   <si>
-    <t>FILE SETTINGS</t>
-  </si>
-  <si>
-    <t>File extension:</t>
-  </si>
-  <si>
-    <t>.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-File extension. 
-Example .csv
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. Change only if the Lumi output files use a different file extension.
-</t>
-  </si>
-  <si>
-    <t>extension</t>
-  </si>
-  <si>
-    <t>Suffix to remove:</t>
-  </si>
-  <si>
-    <t>_Raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Text suffix. 
-Example: _Raw
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. This suffix is removed from raw file names when creating cleaner names.
-</t>
-  </si>
-  <si>
-    <t>suffix_to_remove</t>
-  </si>
-  <si>
-    <t>Raw file suffix:</t>
-  </si>
-  <si>
-    <t>_Raw.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Text suffix. 
-Example: _Raw.csv
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Usually this should not be changed. Change only if the Lumi output files use different names.
-</t>
-  </si>
-  <si>
-    <t>file_suffix</t>
-  </si>
-  <si>
     <t>SAVING</t>
   </si>
   <si>
@@ -605,97 +562,6 @@
   </si>
   <si>
     <t>save_file</t>
-  </si>
-  <si>
-    <t>GROUP-SPECIFIC OVERRIDES</t>
-  </si>
-  <si>
-    <t>Group names:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-List of group names. 
-Example: ["Liver", "Kidney", "Lung"]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Use this section only when you want to override specific settings for specific groups.
-Important Notes:
-NOTE #1: write only the groups for which you want to override at least one setting.
-NOTE #2: each group name MUST be in quotes (example: "Liver").
-NOTE #3: when overriding a setting, maintain the same order in which you listed the groups.Each position matches the group name in the same position.
-For example, if group names are ["Liver", "Kidney", "Lung"], then [500, None, 700] means:
-Liver gets 500, Kidney gets no override, and Lung gets 700.
-</t>
-  </si>
-  <si>
-    <t>override_group_names</t>
-  </si>
-  <si>
-    <t>Y-axis limit:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-List with one value (number/range) per group, or None for no override.
-Example: [500, None, (-100, 500)]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-See section: PLOTTING SETTINGS, setting: Y-axis limit, for a detailed description.
-</t>
-  </si>
-  <si>
-    <t>override_y_limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-List with one value per group, or None for no override. 
-Example: ["Exp. 1", None, None, None]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-See section: PLOTTING SETTINGS, setting: Plot description, for a detailed description.
-</t>
-  </si>
-  <si>
-    <t>override_description</t>
-  </si>
-  <si>
-    <t>Peak label vertical offset:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-List with one value per group, or None for no override. 
-Example: [20, None, None, 35]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-This value is used to adjust the position of the peak text labels.
-</t>
-  </si>
-  <si>
-    <t>override_peak_txt_dy</t>
-  </si>
-  <si>
-    <t>Replicates to hide:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-See examples above.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-For each group choose specific replicates to hide from the plot.
-NOTE: this does NOT exclude them from the calculation of the average signal.
-</t>
-  </si>
-  <si>
-    <t>override_visible_replicate_cols</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1516,34 +1382,34 @@
         <v>78</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="9">
-        <v>2</v>
+        <v>82</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="20" customHeight="1">
@@ -1556,16 +1422,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="9">
-        <v>10</v>
+        <v>87</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>88</v>
@@ -1574,40 +1440,40 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6" t="s">
+    <row r="28" spans="1:6" ht="20" customHeight="1">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="20" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="F29" s="6" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="5" t="s">
-        <v>94</v>
-      </c>
+      <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="9">
-        <v>25</v>
-      </c>
+      <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
         <v>96</v>
       </c>
@@ -1618,219 +1484,83 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6" t="s">
+    <row r="31" spans="1:6" ht="20" customHeight="1">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="B32" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="9">
+        <v>25</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="20" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="E33" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F33" s="6" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="20" customHeight="1">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6" t="s">
+      <c r="B35" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="F35" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="20" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="20" customHeight="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="19">
+  <mergeCells count="16">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A6:F6"/>
@@ -1842,14 +1572,11 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C10">
@@ -1873,13 +1600,13 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C22">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C27">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C35">
       <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>

--- a/settings.xlsx
+++ b/settings.xlsx
@@ -214,8 +214,7 @@
   <si>
     <t xml:space="preserve">
 Choose specific replicates to disable from the analysis.
-NOTE #1: each replicate name must be written inside quotes (" ").
-NOTE #2: write replicate names without suffixes.
+NOTE: each replicate name must be written inside quotes (" ").
 Correct example: ["1a", "2b"]
 Incorrect example: ["1a_Raw.csv", "2b_Raw.csv"]
 </t>
@@ -425,7 +424,7 @@
     <t>show_average_peaks_txt</t>
   </si>
   <si>
-    <t>GROUP-SPECIFIC OVERRIDES</t>
+    <t>SPECIFIC Y-AXIS LIMITS</t>
   </si>
   <si>
     <t>Group names:</t>
@@ -438,8 +437,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-Use this section only when you want to limit Y-axis differently for specific groups.
-For example, if group names are ["Liver", "Lung"], then [500, 700] means:Liver gets 500, and Lung gets 700.
+Use this section only when you want to limit Y-axis differently for specific groups.For example, if group names are ["Liver", "Lung"], then [500, 700] means:Liver gets 500, and Lung gets 700.
 NOTE: each group name MUST be in quotes (example: "Liver").Each position matches the group name in the same position.
 </t>
   </si>
@@ -464,6 +462,91 @@
     <t>override_y_limit</t>
   </si>
   <si>
+    <t>DATA LENGTH / TAIL CUTTING</t>
+  </si>
+  <si>
+    <t>Length of Lumi's interval:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive number. 
+Example: 10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The length of the sampling interval in minutes. 
+NOTE: Lumi's interval by default is 10 minutes.
+</t>
+  </si>
+  <si>
+    <t>interval_minutes</t>
+  </si>
+  <si>
+    <t>Maximum days to analyze:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Positive number, or None.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Limit analysis to the first N days. Leave None for no limit, or choose a positive number N for number of days to analyze.
+This feature is useful to cut the tail of the data if it isn't significant to the analysis.
+</t>
+  </si>
+  <si>
+    <t>max_days</t>
+  </si>
+  <si>
+    <t>ANALYSIS SETTINGS</t>
+  </si>
+  <si>
+    <t>Maximum background noise:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Number. 
+Example: 25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The minimum counts/sec value that marks the beginning of the real signal.All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.
+</t>
+  </si>
+  <si>
+    <t>noise_max</t>
+  </si>
+  <si>
+    <t>Remove background noise:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+•  True = subtract the average pre-sample noise from the signal.
+•  False = keep the signal without subtracting that background.
+</t>
+  </si>
+  <si>
+    <t>remove_noise</t>
+  </si>
+  <si>
+    <t>SAVING</t>
+  </si>
+  <si>
+    <t>Save processed files:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+•  True = save processed files to the given output folder.
+•  False = run analysis without saving files.
+</t>
+  </si>
+  <si>
+    <t>save_file</t>
+  </si>
+  <si>
     <t>PEAK/PERIOD TABLE SETTINGS</t>
   </si>
   <si>
@@ -477,91 +560,6 @@
   </si>
   <si>
     <t>save_peak_tables</t>
-  </si>
-  <si>
-    <t>DATA LENGTH / TAIL CUTTING</t>
-  </si>
-  <si>
-    <t>Length of Lumi's interval:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Positive number. 
-Example: 10
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The length of the sampling interval in minutes. 
-NOTE: Lumi's interval by default is 10 minutes.
-</t>
-  </si>
-  <si>
-    <t>interval_minutes</t>
-  </si>
-  <si>
-    <t>Maximum days to analyze:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Positive number, or None.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Limit analysis to the first N days. Leave None for no limit, or choose a positive number N for number of days to analyze.
-This feature is useful to cut the tail of the data if it isn't significant to the analysis.
-</t>
-  </si>
-  <si>
-    <t>max_days</t>
-  </si>
-  <si>
-    <t>ANALYSIS SETTINGS</t>
-  </si>
-  <si>
-    <t>Maximum background noise:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Number. 
-Example: 25
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The minimum counts/sec value that marks the beginning of the real signal.All consecutive rows from the start, with counts below this threshold, are treated as pre-sample noise.
-</t>
-  </si>
-  <si>
-    <t>noise_max</t>
-  </si>
-  <si>
-    <t>Remove background noise:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-•  True = subtract the average pre-sample noise from the signal.
-•  False = keep the signal without subtracting that background.
-</t>
-  </si>
-  <si>
-    <t>remove_noise</t>
-  </si>
-  <si>
-    <t>SAVING</t>
-  </si>
-  <si>
-    <t>Save processed files:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-•  True = save processed files to the given output folder.
-•  False = run analysis without saving files.
-</t>
-  </si>
-  <si>
-    <t>save_file</t>
   </si>
 </sst>
 </file>
@@ -1427,93 +1425,93 @@
       <c r="B27" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="9">
+        <v>25</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="20" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="20" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="9">
-        <v>25</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="E31" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F32" s="6" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="20" customHeight="1">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
         <v>104</v>
       </c>
@@ -1572,10 +1570,10 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A34:F34"/>
   </mergeCells>
   <dataValidations count="10">
@@ -1600,7 +1598,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C22">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C31">
       <formula1>"True,False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Please choose one of the allowed values." promptTitle="Choose a value" prompt="Choose one of the allowed values." sqref="C33">
